--- a/results/Int All Data 0.8/Linea_fi_all.xlsx
+++ b/results/Int All Data 0.8/Linea_fi_all.xlsx
@@ -1356,7 +1356,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0004420432220039516 +/- 0.0011715972929151745</t>
+          <t>-0.0004911591355599487 +/- 0.0010760757514836088</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.014390962671905672 +/- 0.0031222426474092</t>
+          <t>0.014440078585461657 +/- 0.0031388104732161994</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0038801571709233484 +/- 0.0017770189111125337</t>
+          <t>0.004027504911591329 +/- 0.0017952521495576636</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.0014734774066797796 +/- 0.0010534189876977927</t>
+          <t>-0.0015225933202357655 +/- 0.0010636742547989945</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.005550098231827094 +/- 0.0015998524042143913</t>
+          <t>0.0055992141453830805 +/- 0.0016466654827348058</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0017681728880156954 +/- 0.0009370719070893377</t>
+          <t>0.0017190569744597096 +/- 0.0008854497238369386</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.01538461538461534 +/- 0.0023658094307603015</t>
+          <t>0.01533228676085815 +/- 0.0023871260550407244</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.0022501308215593374 +/- 0.0007418862835561514</t>
+          <t>0.0021978021978021458 +/- 0.0008038875717288012</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.002796833773087104 +/- 0.0008192176620717462</t>
+          <t>0.0031134564643799712 +/- 0.0007985617915789515</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3561,17 +3561,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.006385224274406298 +/- 0.001444214478459533</t>
+          <t>-0.007335092348284944 +/- 0.0016256381847756767</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.00026385224274407817 +/- 0.0012979814117413024</t>
+          <t>0.00021108179419526696 +/- 0.0016213500259353213</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.005857519788918209 +/- 0.0009571692425972313</t>
+          <t>0.006015831134564653 +/- 0.001060672888772671</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.0012664907651715241 +/- 0.00035003955571037286</t>
+          <t>0.0010026385224274348 +/- 0.0004383442671724749</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0012664907651715241 +/- 0.0005381550937829082</t>
+          <t>0.0009498680738786236 +/- 0.00046004210485919167</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.0014248021108179243 +/- 0.0007481502310690296</t>
+          <t>-0.0044327176781002505 +/- 0.00138012631457753</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00026385224274407817 +/- 0.0012979814117413024</t>
+          <t>0.0004221635883905117 +/- 0.0016316226737456707</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.014564643799472265 +/- 0.0013597993379129497</t>
+          <t>-0.014617414248021076 +/- 0.0013360410449785997</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.0016886543535620246 +/- 0.0011752536913625486</t>
+          <t>0.001794195250659647 +/- 0.0011609498680738896</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.013773087071240087 +/- 0.001482276718225662</t>
+          <t>-0.014142480211081776 +/- 0.001543930220403994</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.009182058047493391 +/- 0.0011609498680738874</t>
+          <t>0.009287598944591025 +/- 0.0012752555117250272</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.008865435356200557 +/- 0.0024502768899723085</t>
+          <t>0.008496042216358846 +/- 0.0026007855473037704</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.000844327176780979 +/- 0.0002585213448847609</t>
+          <t>0.0011609498680738794 +/- 0.0004600421048592044</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0016886543535620246 +/- 0.0011752536913625486</t>
+          <t>0.0016886543535620357 +/- 0.0009672982997268393</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.004432717678100284 +/- 0.0018157942516184838</t>
+          <t>0.0036939313984169055 +/- 0.001828021960494851</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>5.277044854882229e-05 +/- 0.0008654997080135496</t>
+          <t>-0.00010554089709761128 +/- 0.0009672982997268188</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-0.001635883905013169 +/- 0.0009571692425972086</t>
+          <t>-0.0014248021108179243 +/- 0.0010300380631104587</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>0.0011609498680738794 +/- 0.00031662269129291155</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.0015831134564644022 +/- 0.0011799831015830192</t>
+          <t>0.002005277044854903 +/- 0.0014120409667820251</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.0011609498680738906 +/- 0.00039489787723211465</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.001635883905013169 +/- 0.0009571692425972086</t>
+          <t>-0.0016358839050131912 +/- 0.0013851614510191773</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>-0.004116094986807373 +/- 0.0023927776356210176</t>
+          <t>-0.0011081794195250572 +/- 0.0016927720245219326</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -3891,79 +3891,79 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>-0.007176781002638499 +/- 0.0029870124956379706</t>
+          <t>2.2204460492503132e-17 +/- 0.003148587628533246</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
+          <t>0.00031662269129286715 +/- 0.0002585213448847609</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>0.0020052770448548917 +/- 0.0011987141627019112</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>0.0004749340369393118 +/- 0.0006860158311345633</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>0.00015831134564644466 +/- 0.0008525326871453056</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>-0.006279683377308698 +/- 0.0016084169555808138</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>-0.0017941952506596026 +/- 0.0018157942516184816</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>-0.006068601583113442 +/- 0.0022911127542050084</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>-0.0007387862796833566 +/- 0.002565751088367956</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>0.00232189973614777 +/- 0.0013182053822476916</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>0.004907651715039596 +/- 0.0015839927197681927</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>0.5237467018469657 +/- 0.009119521367313144</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>0.0008970976253298346 +/- 0.0007099537755712033</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>0.3823746701846966 +/- 0.0104751666496839</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
           <t>0.00026385224274405594 +/- 0.0003539949304748908</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>0.003852242744063328 +/- 0.002574959978629211</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>0.0003693931398416783 +/- 0.0006695819282558927</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>0.0003693931398416783 +/- 0.0006695819282558927</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>-0.006279683377308698 +/- 0.0016084169555808138</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>-0.002585751978891826 +/- 0.0021035494910812474</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>-0.0050659630606859855 +/- 0.0019631741675713325</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>-0.0007387862796833566 +/- 0.002565751088367956</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>0.00232189973614777 +/- 0.0013182053822476916</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>-0.0012137203166226684 +/- 0.0010026385224274341</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>0.5237467018469657 +/- 0.009119521367313144</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>0.0008970976253298346 +/- 0.0007099537755712033</t>
-        </is>
-      </c>
-      <c r="CI5" t="inlineStr">
-        <is>
-          <t>0.3823746701846966 +/- 0.0104751666496839</t>
-        </is>
-      </c>
-      <c r="CJ5" t="inlineStr">
-        <is>
-          <t>0.00031662269129286715 +/- 0.0002585213448847609</t>
-        </is>
-      </c>
       <c r="CK5" t="inlineStr">
         <is>
           <t>-0.0007387862796833678 +/- 0.001006795990941366</t>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>0.005435356200527708 +/- 0.003304374080095696</t>
+          <t>0.00506596306068603 +/- 0.003305637944773807</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>-0.0014248021108179243 +/- 0.0009454603096131437</t>
+          <t>-0.001372031662269102 +/- 0.0006332453825857564</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>0.3567282321899737 +/- 0.006415462972212802</t>
+          <t>0.35699208443271774 +/- 0.0064122066673051705</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>0.03625329815303431 +/- 0.004995385677905594</t>
+          <t>0.03477572559366755 +/- 0.005167463824911707</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>-0.00205804749340367 +/- 0.001676240651637842</t>
+          <t>-0.0016358839050131802 +/- 0.001424802110817942</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>-0.0033773087071239938 +/- 0.0021526203751315214</t>
+          <t>-0.0037994722955145056 +/- 0.002297787974361722</t>
         </is>
       </c>
       <c r="CZ5" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>0.060580474934036954 +/- 0.005865833554233343</t>
+          <t>0.06100263852242745 +/- 0.00567472509077364</t>
         </is>
       </c>
       <c r="DC5" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>0.3567282321899737 +/- 0.006415462972212802</t>
+          <t>0.356622691292876 +/- 0.006475086712476164</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>0.0010026385224274682 +/- 0.000725473724795152</t>
+          <t>0.0011081794195250904 +/- 0.000725473724795152</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>0.0029023746701847043 +/- 0.0014403529355098833</t>
+          <t>0.0034828496042216494 +/- 0.001458604217528786</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>-0.0018469656992084471 +/- 0.0013192612137203309</t>
+          <t>-0.002058047493403692 +/- 0.0011905555855069815</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0002359966203165939</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0002359966203165939</t>
+          <t>0.0 +/- 0.000333749621125941</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
@@ -4141,129 +4141,129 @@
       </c>
       <c r="DT5" t="inlineStr">
         <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DU5" t="inlineStr">
+        <is>
+          <t>0.0011609498680738794 +/- 0.0005683551247635655</t>
+        </is>
+      </c>
+      <c r="DV5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DW5" t="inlineStr">
+        <is>
+          <t>0.0032717678100264045 +/- 0.0009672982997267993</t>
+        </is>
+      </c>
+      <c r="DX5" t="inlineStr">
+        <is>
+          <t>-0.00010554089709762238 +/- 0.00021108179419524476</t>
+        </is>
+      </c>
+      <c r="DY5" t="inlineStr">
+        <is>
+          <t>0.00021108179419527807 +/- 0.0023146925804180805</t>
+        </is>
+      </c>
+      <c r="DZ5" t="inlineStr">
+        <is>
+          <t>0.00010554089709762238 +/- 0.00021108179419524476</t>
+        </is>
+      </c>
+      <c r="EA5" t="inlineStr">
+        <is>
+          <t>-0.0009498680738786125 +/- 0.0009672982997268188</t>
+        </is>
+      </c>
+      <c r="EB5" t="inlineStr">
+        <is>
+          <t>0.0026385224274406483 +/- 0.0014159797218996006</t>
+        </is>
+      </c>
+      <c r="EC5" t="inlineStr">
+        <is>
+          <t>0.005329815303430086 +/- 0.0016256381847756583</t>
+        </is>
+      </c>
+      <c r="ED5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="EE5" t="inlineStr">
+        <is>
+          <t>0.0003693931398416783 +/- 0.00024182457493169984</t>
+        </is>
+      </c>
+      <c r="EF5" t="inlineStr">
+        <is>
+          <t>0.00015831134564643358 +/- 0.00024182457493169982</t>
+        </is>
+      </c>
+      <c r="EG5" t="inlineStr">
+        <is>
+          <t>0.00026385224274405594 +/- 0.00026385224274405594</t>
+        </is>
+      </c>
+      <c r="EH5" t="inlineStr">
+        <is>
+          <t>0.0007915567282322011 +/- 0.0010619847914247083</t>
+        </is>
+      </c>
+      <c r="EI5" t="inlineStr">
+        <is>
+          <t>-0.0022163588390501365 +/- 0.0016486015147032546</t>
+        </is>
+      </c>
+      <c r="EJ5" t="inlineStr">
+        <is>
+          <t>0.00153034300791558 +/- 0.0007985617915789992</t>
+        </is>
+      </c>
+      <c r="EK5" t="inlineStr">
+        <is>
+          <t>-0.00026385224274405594 +/- 0.0005407361881772724</t>
+        </is>
+      </c>
+      <c r="EL5" t="inlineStr">
+        <is>
+          <t>5.277044854881119e-05 +/- 0.00015831134564643355</t>
+        </is>
+      </c>
+      <c r="EM5" t="inlineStr">
+        <is>
+          <t>-0.00010554089709762238 +/- 0.00021108179419524476</t>
+        </is>
+      </c>
+      <c r="EN5" t="inlineStr">
+        <is>
+          <t>-0.0006332453825857454 +/- 0.0009956708318793253</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>0.00021108179419524476 +/- 0.00025852134488476094</t>
+        </is>
+      </c>
+      <c r="EP5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>0.00079155672823219 +/- 0.0005407361881773049</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
           <t>-5.277044854881119e-05 +/- 0.00015831134564643355</t>
         </is>
       </c>
-      <c r="DU5" t="inlineStr">
-        <is>
-          <t>0.0012664907651715241 +/- 0.0005876268456813023</t>
-        </is>
-      </c>
-      <c r="DV5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="DW5" t="inlineStr">
-        <is>
-          <t>0.0032717678100264045 +/- 0.0009672982997267993</t>
-        </is>
-      </c>
-      <c r="DX5" t="inlineStr">
-        <is>
-          <t>-0.00010554089709762238 +/- 0.00021108179419524476</t>
-        </is>
-      </c>
-      <c r="DY5" t="inlineStr">
-        <is>
-          <t>0.00021108179419527807 +/- 0.0023146925804180805</t>
-        </is>
-      </c>
-      <c r="DZ5" t="inlineStr">
-        <is>
-          <t>0.00010554089709762238 +/- 0.00021108179419524476</t>
-        </is>
-      </c>
-      <c r="EA5" t="inlineStr">
-        <is>
-          <t>-0.0009498680738786125 +/- 0.0009672982997268188</t>
-        </is>
-      </c>
-      <c r="EB5" t="inlineStr">
-        <is>
-          <t>0.0029023746701847043 +/- 0.0014403529355098833</t>
-        </is>
-      </c>
-      <c r="EC5" t="inlineStr">
-        <is>
-          <t>0.005329815303430086 +/- 0.0016256381847756583</t>
-        </is>
-      </c>
-      <c r="ED5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="EE5" t="inlineStr">
-        <is>
-          <t>0.0003693931398416783 +/- 0.00024182457493169984</t>
-        </is>
-      </c>
-      <c r="EF5" t="inlineStr">
-        <is>
-          <t>0.00015831134564643358 +/- 0.00024182457493169982</t>
-        </is>
-      </c>
-      <c r="EG5" t="inlineStr">
-        <is>
-          <t>0.0004221635883904895 +/- 0.0003948978772320672</t>
-        </is>
-      </c>
-      <c r="EH5" t="inlineStr">
-        <is>
-          <t>0.0007915567282322011 +/- 0.0010619847914247083</t>
-        </is>
-      </c>
-      <c r="EI5" t="inlineStr">
-        <is>
-          <t>-0.0022163588390501365 +/- 0.0016486015147032546</t>
-        </is>
-      </c>
-      <c r="EJ5" t="inlineStr">
-        <is>
-          <t>0.0009498680738786347 +/- 0.0006591026911238639</t>
-        </is>
-      </c>
-      <c r="EK5" t="inlineStr">
-        <is>
-          <t>-0.00026385224274405594 +/- 0.0005407361881772724</t>
-        </is>
-      </c>
-      <c r="EL5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="EM5" t="inlineStr">
-        <is>
-          <t>-0.00031662269129286715 +/- 0.0007158131908311428</t>
-        </is>
-      </c>
-      <c r="EN5" t="inlineStr">
-        <is>
-          <t>-0.00031662269129286715 +/- 0.0007158131908311428</t>
-        </is>
-      </c>
-      <c r="EO5" t="inlineStr">
-        <is>
-          <t>0.00021108179419524476 +/- 0.00025852134488476094</t>
-        </is>
-      </c>
-      <c r="EP5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="EQ5" t="inlineStr">
-        <is>
-          <t>0.00031662269129286715 +/- 0.0003500395557103226</t>
-        </is>
-      </c>
-      <c r="ER5" t="inlineStr">
-        <is>
-          <t>-5.277044854881119e-05 +/- 0.00015831134564643355</t>
-        </is>
-      </c>
       <c r="ES5" t="inlineStr">
         <is>
           <t>0.0007387862796833566 +/- 0.0003500395557103226</t>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="ET5" t="inlineStr">
         <is>
-          <t>0.0010026385224274458 +/- 0.0005993570813509776</t>
+          <t>0.00026385224274405594 +/- 0.00026385224274405594</t>
         </is>
       </c>
       <c r="EU5" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="EX5" t="inlineStr">
         <is>
-          <t>-0.00026385224274405594 +/- 0.0005407361881772724</t>
+          <t>-0.00031662269129286715 +/- 0.0005876268456812524</t>
         </is>
       </c>
       <c r="EY5" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0020285087719298265 +/- 0.001344040643874037</t>
+          <t>-0.002083333333333337 +/- 0.0013607098296042545</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>0.04078313253012049 +/- 0.003819961171683768</t>
+          <t>0.04084337349397591 +/- 0.003836550199539904</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.040361445783132534 +/- 0.006392358262593876</t>
+          <t>0.04042168674698796 +/- 0.006360772600379657</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -7216,72 +7216,72 @@
       </c>
       <c r="DO9" t="inlineStr">
         <is>
+          <t>0.03484767504008551 +/- 0.0031961339150670433</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>-0.0003206841261357729 +/- 0.0004275788348476972</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>0.0033137359700694423 +/- 0.00032068412613575067</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>0.0036878674505611887 +/- 0.0012523115461101038</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>0.03228220203099943 +/- 0.0036579238123503346</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>-0.0003206841261357729 +/- 0.0005450582056219186</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>-0.0012292891501870739 +/- 0.00041743718203667176</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>0.027151256012827342 +/- 0.002826147315104715</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>-0.0012292891501870739 +/- 0.00041743718203667176</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
           <t>0.034794227685729553 +/- 0.00324623936698242</t>
-        </is>
-      </c>
-      <c r="DP9" t="inlineStr">
-        <is>
-          <t>-0.0003206841261357729 +/- 0.0004275788348476972</t>
-        </is>
-      </c>
-      <c r="DQ9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="DR9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="DS9" t="inlineStr">
-        <is>
-          <t>0.0033137359700694423 +/- 0.00032068412613575067</t>
-        </is>
-      </c>
-      <c r="DT9" t="inlineStr">
-        <is>
-          <t>0.0036878674505611887 +/- 0.0012523115461101038</t>
-        </is>
-      </c>
-      <c r="DU9" t="inlineStr">
-        <is>
-          <t>0.03228220203099943 +/- 0.0036579238123503346</t>
-        </is>
-      </c>
-      <c r="DV9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="DW9" t="inlineStr">
-        <is>
-          <t>-0.0003206841261357729 +/- 0.0005450582056219186</t>
-        </is>
-      </c>
-      <c r="DX9" t="inlineStr">
-        <is>
-          <t>-0.0012292891501870739 +/- 0.00041743718203667176</t>
-        </is>
-      </c>
-      <c r="DY9" t="inlineStr">
-        <is>
-          <t>0.027151256012827342 +/- 0.002826147315104715</t>
-        </is>
-      </c>
-      <c r="DZ9" t="inlineStr">
-        <is>
-          <t>-5.3447354355962154e-05 +/- 0.00016034206306788645</t>
-        </is>
-      </c>
-      <c r="EA9" t="inlineStr">
-        <is>
-          <t>-0.0012292891501870739 +/- 0.00041743718203667176</t>
-        </is>
-      </c>
-      <c r="EB9" t="inlineStr">
-        <is>
-          <t>0.03484767504008551 +/- 0.0031961339150670433</t>
         </is>
       </c>
       <c r="EC9" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.03845752996352268 +/- 0.00412167169010633</t>
+          <t>0.038561750911933326 +/- 0.004188333777469551</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>-5.211047420531356e-05 +/- 0.00036477331943719494</t>
+          <t>-0.00010422094841062712 +/- 0.0003899590814772088</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="DT10" t="inlineStr">
         <is>
-          <t>0.001094319958311618 +/- 0.0011523368622978682</t>
+          <t>0.0010422094841063046 +/- 0.001188301641583265</t>
         </is>
       </c>
       <c r="DU10" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.004168893639764826 +/- 0.002935228266754869</t>
+          <t>-0.004115446285408863 +/- 0.0029083416056467563</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>-0.004115446285408863 +/- 0.002293259000847136</t>
+          <t>-0.004061998931052901 +/- 0.002282646339290501</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
